--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488251_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488251_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>J. RUIZ CORDAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.432</v>
+        <v>5.6782</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0929</v>
+        <v>5.9528</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3391</v>
+        <v>-0.2746</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2915</v>
+        <v>3.0247</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7783</v>
+        <v>3.6681</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.4868</v>
+        <v>-0.6434</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9173</v>
+        <v>3.5981</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1815</v>
+        <v>4.1265</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.2643</v>
+        <v>-0.5284</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6258</v>
+        <v>-0.5734</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4033</v>
+        <v>-0.4584</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2226</v>
+        <v>-0.115</v>
       </c>
       <c r="P2" t="n">
+        <v>-0.1853</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-1.1117</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.9264</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-0.9264</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.8529</v>
-      </c>
       <c r="S2" t="n">
-        <v>1.6402</v>
+        <v>-0.3078</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2137</v>
+        <v>-0.309</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4265</v>
+        <v>0.0012</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5738</v>
+        <v>3.1466</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8883</v>
+        <v>3.7755</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3144</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RUIZ CORDAL</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.361</v>
+        <v>5.5369</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0939</v>
+        <v>4.3209</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2671</v>
+        <v>1.216</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0247</v>
+        <v>2.2915</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6681</v>
+        <v>3.7783</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6434</v>
+        <v>-1.4868</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5981</v>
+        <v>2.9173</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1265</v>
+        <v>4.1815</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5284</v>
+        <v>-1.2643</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5734</v>
+        <v>-0.6258</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4584</v>
+        <v>-0.4033</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.115</v>
+        <v>-0.2226</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1853</v>
+        <v>0.9264</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1117</v>
+        <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9264</v>
+        <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>0.375</v>
+        <v>0.7452</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1679</v>
+        <v>0.4418</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5429</v>
+        <v>0.3034</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1466</v>
+        <v>1.5738</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7755</v>
+        <v>1.8883</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6289</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0334</v>
+        <v>2.1324</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9534</v>
+        <v>3.2247</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.92</v>
+        <v>-1.0923</v>
       </c>
       <c r="G4" t="n">
         <v>3.5208</v>
@@ -766,13 +766,13 @@
         <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5863</v>
+        <v>0.6852</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9401</v>
+        <v>0.2114</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6461</v>
+        <v>0.4738</v>
       </c>
       <c r="V4" t="n">
         <v>-1.8883</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.12</v>
+        <v>1.9592</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7762</v>
+        <v>1.4185</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3438</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>2.7188</v>
@@ -844,13 +844,13 @@
         <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2838</v>
+        <v>-0.4446</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8207</v>
+        <v>-0.1784</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4631</v>
+        <v>-0.2661</v>
       </c>
       <c r="V5" t="n">
         <v>-0.315</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0939</v>
+        <v>0.1677</v>
       </c>
       <c r="E8" t="n">
         <v>1.0465</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9526</v>
+        <v>-0.8787</v>
       </c>
       <c r="G8" t="n">
         <v>0.4888</v>
@@ -1078,13 +1078,13 @@
         <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.136</v>
+        <v>-0.0622</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0266</v>
+        <v>0.0473</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6294</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PINA GUISADO</t>
+          <t>I. GARCIA REYES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0385</v>
+        <v>0.0098</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1862</v>
+        <v>-0.2306</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2247</v>
+        <v>0.2404</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1104</v>
+        <v>0.3128</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1288</v>
+        <v>-0.4706</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0185</v>
+        <v>0.7834</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1048</v>
+        <v>0.0429</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.0429</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0056</v>
+        <v>0.2699</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6354</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6299</v>
+        <v>0.7834</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0157</v>
+        <v>-0.618</v>
       </c>
       <c r="T9" t="n">
-        <v>0.291</v>
+        <v>-0.2736</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2753</v>
+        <v>-0.3445</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3144</v>
+        <v>0.315</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3144</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. GARCIA REYES</t>
+          <t>J. PINA GUISADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0641</v>
+        <v>-0.3564</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2306</v>
+        <v>-0.2055</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1665</v>
+        <v>-0.1509</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3128</v>
+        <v>-0.1104</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4706</v>
+        <v>-0.1288</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7834</v>
+        <v>0.0185</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0429</v>
+        <v>-0.1048</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0429</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2699</v>
+        <v>-0.0056</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.6354</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7834</v>
+        <v>0.6299</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6919</v>
+        <v>-0.3022</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2736</v>
+        <v>-0.1007</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4183</v>
+        <v>-0.2015</v>
       </c>
       <c r="V10" t="n">
-        <v>0.315</v>
+        <v>-0.3144</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.315</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. SAENZ - DIAZ MURO</t>
+          <t>M. TRILLO MANGANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8493000000000001</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5843</v>
+        <v>-0.5997</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4336</v>
+        <v>-0.0883</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2666</v>
+        <v>-0.9385</v>
       </c>
       <c r="H11" t="n">
-        <v>0.159</v>
+        <v>0.2826</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1076</v>
+        <v>-1.2211</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1503</v>
+        <v>-0.6314</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1503</v>
+        <v>0.0215</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.6529</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1163</v>
+        <v>-0.3071</v>
       </c>
       <c r="N11" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.2611</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1076</v>
+        <v>-0.5683</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0985</v>
+        <v>0.0653</v>
       </c>
       <c r="T11" t="n">
-        <v>0.434</v>
+        <v>0.0317</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5325</v>
+        <v>0.0336</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. TRILLO MANGANO</t>
+          <t>C. SAENZ - DIAZ MURO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.037</v>
+        <v>-1.0446</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8502</v>
+        <v>0.2905</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1868</v>
+        <v>-1.3351</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9385</v>
+        <v>0.2666</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2826</v>
+        <v>0.159</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2211</v>
+        <v>0.1076</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6314</v>
+        <v>0.1503</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0215</v>
+        <v>0.1503</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6529</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3071</v>
+        <v>0.1163</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2611</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5683</v>
+        <v>0.1076</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2838</v>
+        <v>-0.2938</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2189</v>
+        <v>0.1402</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0649</v>
+        <v>-0.434</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.196</v>
+        <v>-1.2791</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.561</v>
+        <v>-0.5702</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.635</v>
+        <v>-0.7089</v>
       </c>
       <c r="G13" t="n">
         <v>0.2225</v>
@@ -1468,13 +1468,13 @@
         <v>2.594</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7531</v>
+        <v>0.1638</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0732</v>
+        <v>-0.0824</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3201</v>
+        <v>0.2462</v>
       </c>
       <c r="V13" t="n">
         <v>-3.1477</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.2076</v>
+        <v>-2.9213</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.9172</v>
+        <v>-2.9264</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2904</v>
+        <v>0.0051</v>
       </c>
       <c r="G14" t="n">
         <v>-3.0114</v>
@@ -1546,13 +1546,13 @@
         <v>2.2234</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9929</v>
+        <v>-0.7066</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3467</v>
+        <v>-0.3559</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6462</v>
+        <v>-0.3507</v>
       </c>
       <c r="V14" t="n">
         <v>-0.315</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.5581</v>
+        <v>11.1051</v>
       </c>
       <c r="E15" t="n">
-        <v>13.0847</v>
+        <v>13.6318</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5266</v>
+        <v>-2.5265</v>
       </c>
       <c r="G15" t="n">
         <v>10.6965</v>
@@ -1609,7 +1609,7 @@
         <v>-5.8811</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.9614</v>
+        <v>-4.961399999999999</v>
       </c>
       <c r="O15" t="n">
         <v>-0.9198000000000001</v>
@@ -1624,10 +1624,10 @@
         <v>12.9702</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.622799999999999</v>
+        <v>-1.0757</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1316</v>
+        <v>-0.5842999999999999</v>
       </c>
       <c r="U15" t="n">
         <v>-0.4913</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9788</v>
+        <v>3.1877</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3279</v>
+        <v>2.2093</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6509</v>
+        <v>0.9785</v>
       </c>
       <c r="G16" t="n">
         <v>2.6157</v>
@@ -1702,13 +1702,13 @@
         <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8857</v>
+        <v>-0.6768</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3679</v>
+        <v>-0.4865</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5178</v>
+        <v>-0.1903</v>
       </c>
       <c r="V16" t="n">
         <v>0.6929999999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. CASAS GARCIA</t>
+          <t>B. LEÓN TEJERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1481</v>
+        <v>0.6221</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5405</v>
+        <v>0.6221</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3924</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.0737</v>
+        <v>0.6221</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.063</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0107</v>
+        <v>0.6221</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.281</v>
+        <v>0.6221</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4469</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1659</v>
+        <v>0.6221</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7927</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6161</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1766</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4801</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1926</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2875</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. LEÓN TEJERA</t>
+          <t>S. CASAS GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6221</v>
+        <v>0.2662</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6221</v>
+        <v>0.757</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.4909</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6221</v>
+        <v>-2.0737</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-2.063</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6221</v>
+        <v>-0.0107</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6221</v>
+        <v>-0.281</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.4469</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6221</v>
+        <v>0.1659</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.7927</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.6161</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.1766</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.5981</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.4091</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5048</v>
+        <v>-0.0587</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4101</v>
+        <v>0.9205</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9053</v>
+        <v>-0.9792</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4246</v>
@@ -1936,13 +1936,13 @@
         <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7029</v>
+        <v>1.1394</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1254</v>
+        <v>0.6358</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5775</v>
+        <v>0.5036</v>
       </c>
       <c r="V19" t="n">
         <v>1.6352</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1348</v>
+        <v>-0.0775</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1577</v>
+        <v>0.0598</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2926</v>
+        <v>-0.1374</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2271</v>
@@ -2014,13 +2014,13 @@
         <v>0.1853</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.093</v>
+        <v>-0.0358</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0037</v>
+        <v>-0.1016</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0893</v>
+        <v>0.0659</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9854</v>
+        <v>-0.4318</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7555</v>
+        <v>2.6369</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.741</v>
+        <v>-3.0687</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2417</v>
@@ -2092,13 +2092,13 @@
         <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.2155</v>
+        <v>-0.6619</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3803</v>
+        <v>-0.4989</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.1629</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1959</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>M. CASERO MIGLIAVACCA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0692</v>
+        <v>-2.2211</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1614</v>
+        <v>1.3111</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-3.5322</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3495</v>
+        <v>-4.9441</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9378</v>
+        <v>-1.904</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2872</v>
+        <v>-3.0401</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0552</v>
+        <v>-2.4378</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1429</v>
+        <v>0.1416</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.0877</v>
+        <v>-2.5794</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4047</v>
+        <v>-2.5063</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.2051</v>
+        <v>-2.0455</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1996</v>
+        <v>-0.4607</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.3352</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.6322</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.297</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5524</v>
+        <v>0.2783</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1567</v>
+        <v>-0.0276</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3957</v>
+        <v>0.3059</v>
       </c>
       <c r="V22" t="n">
-        <v>0.063</v>
+        <v>1.8888</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2589</v>
+        <v>3.7766</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1959</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. CASERO MIGLIAVACCA</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3437</v>
+        <v>-2.8743</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2132</v>
+        <v>-1.1614</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5568</v>
+        <v>-1.7129</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.9441</v>
+        <v>-0.3495</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.904</v>
+        <v>0.9378</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0401</v>
+        <v>-1.2872</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.4378</v>
+        <v>2.0552</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1416</v>
+        <v>3.1429</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.5794</v>
+        <v>-1.0877</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5063</v>
+        <v>-2.4047</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.0455</v>
+        <v>-2.2051</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4607</v>
+        <v>-0.1996</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5558999999999999</v>
+        <v>-3.3352</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-4.6322</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1557</v>
+        <v>0.7474</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1256</v>
+        <v>0.1567</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2813</v>
+        <v>0.5907</v>
       </c>
       <c r="V23" t="n">
-        <v>1.8888</v>
+        <v>0.063</v>
       </c>
       <c r="W23" t="n">
-        <v>3.7766</v>
+        <v>1.2589</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.8877</v>
+        <v>-1.1959</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0876</v>
+        <v>-2.9886</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0952</v>
+        <v>-1.1931</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9924</v>
+        <v>-1.7954</v>
       </c>
       <c r="G24" t="n">
         <v>-4.1402</v>
@@ -2326,13 +2326,13 @@
         <v>0.1853</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.6519</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4216</v>
+        <v>0.3236</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1313</v>
+        <v>0.3283</v>
       </c>
       <c r="V24" t="n">
         <v>0.3144</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1911</v>
+        <v>-5.3291</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2437</v>
+        <v>-3.6355</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9473</v>
+        <v>-1.6936</v>
       </c>
       <c r="G25" t="n">
         <v>-1.5334</v>
@@ -2404,13 +2404,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3731</v>
+        <v>0.235</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4726</v>
+        <v>0.0809</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.1542</v>
       </c>
       <c r="V25" t="n">
         <v>-0.8809</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.558</v>
+        <v>-9.905100000000001</v>
       </c>
       <c r="E26" t="n">
         <v>2.5267</v>
       </c>
       <c r="F26" t="n">
-        <v>-13.0847</v>
+        <v>-12.4318</v>
       </c>
       <c r="G26" t="n">
         <v>-10.6965</v>
@@ -2482,16 +2482,16 @@
         <v>8.337999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>1.6229</v>
+        <v>2.2756</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4914000000000002</v>
+        <v>0.4915000000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>1.1315</v>
+        <v>1.7844</v>
       </c>
       <c r="V26" t="n">
-        <v>3.147599999999999</v>
+        <v>3.1476</v>
       </c>
       <c r="W26" t="n">
         <v>9.124299999999998</v>
